--- a/.yuleosh/reports/misra-report.xlsx
+++ b/.yuleosh/reports/misra-report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,27 @@
           <t>Status</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>nofile</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>information</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Active checkers: 309/1056 (use --checkers-report=&lt;filename&gt; to see details) [checkersReport]</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
